--- a/dataset_t6_grouped/results2/G4/G4_T6321_W0022F0001T0006Z000C1N3_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T6321_W0022F0001T0006Z000C1N3_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>20.42873303974783</v>
+        <v>3.319669118959023</v>
       </c>
       <c r="D2" t="n">
-        <v>19.08227723075305</v>
+        <v>3.10087004999737</v>
       </c>
       <c r="E2" t="n">
-        <v>12.17010879045841</v>
+        <v>1.977642678449491</v>
       </c>
       <c r="F2" t="n">
-        <v>13.17664234073384</v>
+        <v>2.141204380369248</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>24.58124323148225</v>
+        <v>3.994452025115865</v>
       </c>
       <c r="D3" t="n">
-        <v>2.96742757573518</v>
+        <v>0.4822069810569667</v>
       </c>
       <c r="E3" t="n">
-        <v>12.17010879045841</v>
+        <v>1.977642678449491</v>
       </c>
       <c r="F3" t="n">
-        <v>13.17664234073384</v>
+        <v>2.141204380369248</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>13.73124308002505</v>
+        <v>2.231327000504071</v>
       </c>
       <c r="D4" t="n">
-        <v>11.11414154035101</v>
+        <v>1.806048000307039</v>
       </c>
       <c r="E4" t="n">
-        <v>12.17010879045841</v>
+        <v>1.977642678449491</v>
       </c>
       <c r="F4" t="n">
-        <v>13.17664234073384</v>
+        <v>2.141204380369248</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>36.91102035337888</v>
+        <v>5.998040807424069</v>
       </c>
       <c r="D5" t="n">
-        <v>29.86909428584438</v>
+        <v>4.853727821449712</v>
       </c>
       <c r="E5" t="n">
-        <v>12.17010879045841</v>
+        <v>1.977642678449491</v>
       </c>
       <c r="F5" t="n">
-        <v>13.17664234073384</v>
+        <v>2.141204380369248</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>47.77082510652728</v>
+        <v>7.762759079810682</v>
       </c>
       <c r="D6" t="n">
-        <v>40.06825242767283</v>
+        <v>6.511091019496836</v>
       </c>
       <c r="E6" t="n">
-        <v>12.17010879045841</v>
+        <v>1.977642678449491</v>
       </c>
       <c r="F6" t="n">
-        <v>13.17664234073384</v>
+        <v>2.141204380369248</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
